--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,6 +771,16 @@
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -778,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,6 +879,16 @@
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92790</v>
+        <v>92792</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92844</v>
+        <v>92849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92849</v>
+        <v>92857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128675840</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128676174</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,32 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128675840</v>
+        <v>128804347</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>5179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>674679</v>
+        <v>674637</v>
       </c>
       <c r="R3" t="n">
-        <v>6564816</v>
+        <v>6564804</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -855,17 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett flertal exemplar.</t>
+          <t>Gnagspår på en gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,6 +890,114 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128675840</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vidja, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>674679</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6564816</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett flertal exemplar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17467-2024 artfynd.xlsx
+++ b/artfynd/A 17467-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128676174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128804347</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,8 +1013,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675840</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>